--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/demitas.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/demitas.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Deuses e seres antigos são arrogantes. Sua existência prolongada distorceu até mesmo os princípios do mundo.</t>
+          <t>Deuses e seres antigos são arrogantes. A existência prolongada deles deformou até os princípios do mundo.</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Eu tenho algumas perguntas.</t>
+          <t>Tenho algumas perguntas.</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>Você deseja o meu conhecimento?</t>
+          <t>Buscas o meu conhecimento?</t>
         </is>
       </c>
       <c r="M15" s="9" t="n"/>
@@ -593,7 +593,7 @@
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>Sobre a reserva de Livro de Feitiços</t>
+          <t>Sobre reserva de livros de feitiço</t>
         </is>
       </c>
       <c r="M16" s="9" t="n"/>
@@ -731,9 +731,9 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>Bem... Você se interessa por magia?
-Se você tem um livro de magia que deseja reproduzir, deixe-o comigo. É uma tarefa árdua copiar livros de magia, pois cada runa deve ser decifrada palavra por palavra. Se eu o considerar digno de minha atenção, talvez eu considere adequado criar uma cópia.
-Algumas delas são difíceis de decifrar, mas com tempo suficiente deve ser possível duplicá-las.</t>
+          <t>Bom... estás intrigado com a magia, não estás?
+Se há um livro de feitiço que desejas ver copiado, deixe comigo. Decifrar cada runa, de um tomo tão arcano, leva tempo. Se eu julgá-lo digno da minha atenção, talvez me disponha a criar uma cópia.
+Há livros raros que até eu preciso labutar sobre eles, mas com tempo suficiente, uma cópia impecável certamente estará ao meu alcance.</t>
         </is>
       </c>
       <c r="M22" s="9" t="n"/>
@@ -793,8 +793,8 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>... #pc? Tenho uma história para lhe contar.
-Certa vez, quando eu era um homem, aprofundei meu estudo das runas e dominei a arte de transcrever livros mágicos antigos. Essa é uma habilidade rara, que ninguém na Terra conhece atualmente.</t>
+          <t>...#pc, tenho palavras para ti.
+Em tempos idos, quando ainda tinha a forma de um homem mortal, mergulhei fundo nas runas e dominei a arte de escrever feitiços. Uma perícia rara hoje perdida para os que habitam a terra.</t>
         </is>
       </c>
     </row>
@@ -816,8 +816,8 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Eu o tenho observado de longe desde que me instalei neste lugar, mas se você for confrontar Issizzle, precisará do meu conhecimento.
-... Se quiser ajuda com sua magia, venha até mim.</t>
+          <t>Desde que tomei morada neste lugar, busquei vigiar-te de longe, mas se pretendes enfrentar Issizzle, meu conhecimento será de suma necessidade.
+...Se buscares a ajuda da magia, vem até mim.</t>
         </is>
       </c>
     </row>
